--- a/AAII_Financials/Quarterly/CTVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTVA_QTR_FIN.xlsx
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6379000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4905000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3910000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2618000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6456000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4417000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3978000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2326000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6112000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4492000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3707000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2590000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6045000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4884000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3825000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2777000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6252000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4601000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3479000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2371000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5627000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4178000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3207000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1863000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5191000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3956000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2983000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1911000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5556000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3396000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1947000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5731000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3794000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2678000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2718000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2372000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2254000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1644000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2932000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2342000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2496000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1565000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2918000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2550000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2407000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1643000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3103000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2768000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2510000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1879000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3323000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2724000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2232000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1558000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3010000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2420000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2112000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1297000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2829000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2269000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1968000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1349000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3047000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2211000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2024000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1485000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3687000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2752000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1804000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3661000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2533000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1656000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>974000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3524000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2075000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1482000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>761000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3194000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1942000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1300000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>947000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2942000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2116000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1315000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>898000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2929000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1877000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1247000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>813000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2617000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1758000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1095000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>566000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2362000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1687000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1015000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>562000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2509000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1185000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>791000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>462000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2044000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1042000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>874000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,115 +1180,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E12" s="3">
         <v>341000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>413000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>351000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>375000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>335000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>365000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>348000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>357000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>332000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>357000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>335000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>329000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>316000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>340000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>312000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>296000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>268000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>316000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>297000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>293000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>281000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>305000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>284000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>273000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>280000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>290000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>289000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>269000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>299000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>345000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>325000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>354000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>331000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>383000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1381,165 +1398,171 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E14" s="3">
         <v>232000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>633000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>37000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-32000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>18000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>28000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>32000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>126000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>125000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>219000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>61000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>138000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>45000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>62000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>136000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>139000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>25000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>134000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>48000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>163000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>116000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>32000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>196000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>401000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>286000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>577000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4990000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>318000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>323000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E15" s="3">
         <v>160000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>159000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>162000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>161000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>162000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>164000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>170000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>174000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>177000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>175000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>174000</v>
       </c>
       <c r="O15" s="3">
         <v>174000</v>
       </c>
       <c r="P15" s="3">
+        <v>174000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>160000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>166000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>178000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>179000</v>
       </c>
       <c r="T15" s="3">
         <v>179000</v>
@@ -1548,55 +1571,58 @@
         <v>179000</v>
       </c>
       <c r="V15" s="3">
-        <v>180000</v>
+        <v>179000</v>
       </c>
       <c r="W15" s="3">
         <v>180000</v>
       </c>
       <c r="X15" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>183000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>181000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>162000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>176000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>163000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>161000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>100000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>113000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>101000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>107000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>88000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>107000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>89000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4457000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3743000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3691000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2888000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4630000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3596000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3795000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2791000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4539000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3831000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3702000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2852000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4681000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3993000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3842000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3162000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4954000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3914000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3542000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2732000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4615000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3717000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3332000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2388000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4406000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3585000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3198000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2580000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4767000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3632000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3747000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7521000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5431000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4244000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3186000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1922000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1162000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>219000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-270000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1826000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>821000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>183000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-465000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1573000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>661000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-262000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1364000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>891000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-385000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1298000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>687000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-63000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-361000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1012000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>461000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-125000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-525000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>785000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>371000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-215000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-669000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>789000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-236000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-932000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-5574000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>300000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-450000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-508000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1884,543 +1917,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E20" s="3">
         <v>70000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>114000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>46000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>33000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>46000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>103000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>68000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>48000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>177000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>122000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>114000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>79000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-150000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>45000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>20000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>316000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>377000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>297000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>337000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>65000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>29000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>73000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>47000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>52000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>57000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>44000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>104000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>6000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2007000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1252000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>264000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-154000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1954000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>968000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>301000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-398000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1679000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>790000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-210000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1424000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>972000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>137000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-68000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1645000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1014000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>570000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>325000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1622000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1102000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>249000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-211000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1158000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>701000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>126000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-386000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1145000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>534000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-130000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-4886000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1806000</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E22" s="3">
         <v>36000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>46000</v>
       </c>
       <c r="F22" s="3">
         <v>46000</v>
       </c>
       <c r="G22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="H22" s="3">
         <v>52000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>36000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>60000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>66000</v>
       </c>
       <c r="K22" s="3">
         <v>66000</v>
       </c>
       <c r="L22" s="3">
+        <v>66000</v>
+      </c>
+      <c r="M22" s="3">
         <v>41000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>62000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>58000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>82000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>31000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>36000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>8000</v>
       </c>
       <c r="V22" s="3">
         <v>8000</v>
       </c>
       <c r="W22" s="3">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="X22" s="3">
         <v>7000</v>
       </c>
       <c r="Y22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>10000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>14000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>19000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>34000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>59000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>86000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>82000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>88000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>81000</v>
       </c>
-      <c r="AK22" s="3" t="s">
+      <c r="AL22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1625000</v>
+      </c>
+      <c r="E23" s="3">
         <v>858000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-530000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-370000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1804000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>784000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>88000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-633000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1338000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>482000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-323000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-444000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1084000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>776000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-203000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-396000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1327000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>698000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>245000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1302000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>791000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-507000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>844000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>408000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-187000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-631000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>753000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-251000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5650000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>308000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-550000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-481000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>408000</v>
+      </c>
+      <c r="E24" s="3">
         <v>133000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-62000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>422000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>117000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>138000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-114000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>282000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>106000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-92000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-129000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>204000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>169000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-162000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-74000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>325000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>121000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>90000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-28000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>284000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>178000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-169000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-117000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>78000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>127000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-145000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-104000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>270000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>156000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-67000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-112000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-2675000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1217000</v>
+      </c>
+      <c r="E26" s="3">
         <v>725000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-537000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-308000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1382000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>667000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-50000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-519000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1056000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>376000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-231000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-315000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>880000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>607000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-41000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-322000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1002000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>577000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>155000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>36000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1018000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>613000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>99000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-390000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>766000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>281000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-42000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-527000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>483000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-184000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1070000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5642000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>375000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-438000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2194000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1161000</v>
+      </c>
+      <c r="E27" s="3">
         <v>720000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-552000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-320000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1314000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>652000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-524000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1053000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>419000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-253000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-321000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>714000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>595000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-43000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-325000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>999000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>574000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>153000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>34000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1015000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>610000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>97000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-392000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>760000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>271000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-45000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-516000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>469000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-196000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1079000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5647000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>371000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-458000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2188000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,115 +2905,121 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-2000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-12000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-10000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-66000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-11000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>11000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-2000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>47000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-20000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-3000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-163000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-12000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-6000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-30000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-10000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>6000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-4000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-45000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-56000</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>1000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>24000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>22000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>360000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>548000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>526000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>323000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>351000</v>
       </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AL29" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,222 +3235,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-109000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-70000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-114000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-46000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-33000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-46000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-103000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-68000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-48000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-177000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-122000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-114000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>150000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-45000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-20000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-316000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-377000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-297000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-337000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-65000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-52000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-57000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-104000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-96000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>19000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1161000</v>
+      </c>
+      <c r="E33" s="3">
         <v>720000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-552000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-320000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1314000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>652000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-524000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1053000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>419000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-253000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-321000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>714000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>595000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-55000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-331000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>969000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>564000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>159000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>970000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>600000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>41000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-392000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>760000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>272000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-494000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-608000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>164000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-531000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5121000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>694000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-107000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2188000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1161000</v>
+      </c>
+      <c r="E35" s="3">
         <v>720000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-552000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-320000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1314000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>652000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-524000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1053000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>419000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-253000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-321000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>714000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>595000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-55000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-331000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>969000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>564000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>159000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>970000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>600000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>41000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-392000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>760000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>272000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-494000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-608000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>164000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-531000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5121000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>694000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-107000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2188000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,971 +3872,999 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2365000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1964000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4521000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2509000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2065000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2008000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3106000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2421000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1839000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1505000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2644000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2254000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2563000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1646000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3191000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2199000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2401000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2031000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4459000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2779000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2861000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2404000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3526000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2768000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2809000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1963000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1764000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1980000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2077000</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH41" s="3">
         <v>2270000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1657000</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>2000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>77000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>76000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>63000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>72000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>120000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>153000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>98000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>108000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>53000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>85000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>124000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>119000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>254000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>290000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>86000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>103000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>39000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>114000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>269000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>152000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>60000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>10000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>117000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>6000</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH42" s="3">
         <v>5000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>142000</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8305000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8702000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6405000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7817000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8705000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8324000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5706000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6680000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7644000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7934000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5515000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6608000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7982000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8704000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5701000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6273000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6947000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7275000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4811000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5818000</v>
-      </c>
-      <c r="W43" s="3">
-        <v>6792000</v>
       </c>
       <c r="X43" s="3">
         <v>6792000</v>
       </c>
       <c r="Y43" s="3">
+        <v>6792000</v>
+      </c>
+      <c r="Z43" s="3">
         <v>4926000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5627000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6772000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6775000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5528000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6574000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7434000</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH43" s="3">
         <v>5260000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6547000</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4443000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5202000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5667000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5310000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4316000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5132000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5432000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5674000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4893000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6183000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6899000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6320000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5628000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6585000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6811000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5415000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4184000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4986000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5180000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4417000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3541000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4321000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4882000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4374000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3589000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4401000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5032000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4403000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3918000</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH44" s="3">
         <v>5310000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4898000</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ44" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK44" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>990000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1338000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>733000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>725000</v>
       </c>
-      <c r="G45" s="3">
-        <v>842000</v>
-      </c>
       <c r="H45" s="3">
+        <v>590000</v>
+      </c>
+      <c r="I45" s="3">
         <v>1122000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>790000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>802000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>863000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1388000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1104000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1043000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>981000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1309000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>968000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1039000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>978000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1296000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1010000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1029000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1052000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1405000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1165000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1167000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1192000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1530000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1190000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1043000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1086000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH45" s="3">
         <v>10127000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>10096000</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16357000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17385000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17335000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16438000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16004000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16587000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15097000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15649000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15359000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17163000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16260000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16333000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17207000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18329000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16795000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15045000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14764000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15878000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15546000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14146000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14285000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15036000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14768000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14088000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14422000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14679000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13519000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14117000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14521000</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH46" s="3">
         <v>22972000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>23340000</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E47" s="3">
         <v>188000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>182000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>162000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>161000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>235000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>231000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>234000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>215000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>226000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>115000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>106000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>83000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>114000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>102000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>91000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>93000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>91000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>76000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>67000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>68000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>64000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>66000</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>62000</v>
       </c>
       <c r="AA47" s="3">
         <v>62000</v>
       </c>
       <c r="AB47" s="3">
+        <v>62000</v>
+      </c>
+      <c r="AC47" s="3">
         <v>64000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>66000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>70000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>64000</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH47" s="3">
         <v>138000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>144000</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ47" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4178000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4183000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4631000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4202000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4153000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4105000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4513000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4210000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4155000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4206000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4699000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4320000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4306000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4271000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4254000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4185000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4300000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4333000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4329000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4310000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4341000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4299000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4396000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4273000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4293000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4358000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5101000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5046000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4543000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH48" s="3">
         <v>4544000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4384000</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18443000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18556000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18766000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18940000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19101000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19050000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19284000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19713000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19728000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19999000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20231000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20236000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20524000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20645000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19301000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19252000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19660000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19974000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>20151000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>20355000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>20620000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>20730000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>21016000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>21024000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>21139000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>21268000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>21653000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21835000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>22081000</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH49" s="3">
         <v>22248000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>22341000</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5080,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2073000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1928000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1528000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1941000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1814000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1660000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1225000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1465000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1398000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1413000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1040000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1494000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1479000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1570000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2166000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2078000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2089000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2357000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2242000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2244000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2182000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2420000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2403000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2243000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2264000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2609000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2058000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2167000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2789000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH52" s="3">
         <v>58781000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>59439000</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41642000</v>
+      </c>
+      <c r="E54" s="3">
         <v>42717000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42845000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42198000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>41759000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42123000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40825000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>41908000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41464000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43625000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>42996000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43110000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>44189000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45500000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42618000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40651000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>40906000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42633000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>42344000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>41122000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>41496000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>42549000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>42649000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>41690000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>42180000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>42978000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>42397000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>43235000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>43998000</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH54" s="3">
         <v>108683000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>109648000</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,436 +5492,449 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3958000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4187000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4398000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4337000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3828000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3905000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4039000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3753000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3606000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4280000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3678000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3379000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3957000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4895000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4140000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3567000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3685000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4126000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3512000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3070000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3098000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3615000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2994000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2891000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3021000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3702000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3014000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3139000</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH57" s="3">
         <v>3798000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3642000</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3193000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1674000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1016000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2685000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1942000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2291000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>884000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3741000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2253000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2148000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>329000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3609000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3023000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3787000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>24000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1376000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>712000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1018000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>17000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>822000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>527000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1220000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>928000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>674000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1921000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3455000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2058000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH58" s="3">
         <v>2154000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4371000</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ58" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>779000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3599000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3789000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>887000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>937000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2982000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3569000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>791000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>964000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3079000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3652000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>887000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1276000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3109000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5825000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3402000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3577000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4950000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5415000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3471000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3655000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4681000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4930000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3812000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3964000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4257000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4529000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2524000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3417000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH59" s="3">
         <v>7358000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5229000</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10789000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11854000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12125000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10420000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9516000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11481000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10386000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10424000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8953000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11332000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10409000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10348000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10346000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13231000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10744000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8918000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7856000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9653000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9558000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7805000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7252000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8999000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8548000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7734000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7529000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9199000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8238000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8993000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8614000</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH60" s="3">
         <v>13310000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>13242000</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5799,64 +5942,64 @@
         <v>1682000</v>
       </c>
       <c r="E61" s="3">
+        <v>1682000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1979000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1688000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1687000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1792000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2295000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1975000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2471000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2492000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2646000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2290000</v>
       </c>
       <c r="O61" s="3">
         <v>2290000</v>
       </c>
       <c r="P61" s="3">
+        <v>2290000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>1241000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1283000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1277000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1283000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1154000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1100000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>1101000</v>
       </c>
       <c r="W61" s="3">
         <v>1101000</v>
       </c>
       <c r="X61" s="3">
-        <v>1102000</v>
+        <v>1101000</v>
       </c>
       <c r="Y61" s="3">
         <v>1102000</v>
@@ -5868,144 +6011,150 @@
         <v>1102000</v>
       </c>
       <c r="AB61" s="3">
+        <v>1102000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>614000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>115000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>116000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>117000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>5784000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10215000</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1837000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1785000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1545000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1918000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1604000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1251000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1446000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1450000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1483000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1188000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1598000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1615000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1589000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5050000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5372000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5696000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5890000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6063000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7237000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7518000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7670000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7936000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8508000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8748000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9086000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9489000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8865000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9124000</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH62" s="3">
         <v>14436000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>14192000</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16239000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18112000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18459000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16737000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15608000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17596000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16795000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16929000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16043000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18617000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17717000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17643000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17728000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19661000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17316000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15807000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15075000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16937000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16960000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16382000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16111000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18011000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17825000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17584000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17619000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19153000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18088000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>18220000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>18112000</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH66" s="3">
         <v>34023000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>38152000</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,106 +7070,109 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1224000</v>
+      </c>
+      <c r="E72" s="3">
         <v>436000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-67000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>834000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1532000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>587000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>55000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>98000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>992000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>302000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-41000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>325000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1013000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>487000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>250000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>614000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1252000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>750000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>524000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>666000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>941000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>268000</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
-      </c>
       <c r="Z72" s="3">
         <v>0</v>
       </c>
       <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="3">
         <v>508000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-155000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-425000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-397000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>97000</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AH72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI72" s="3" t="s">
-        <v>16</v>
+      <c r="AH72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI72" s="3">
+        <v>0</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>16</v>
@@ -7006,8 +7180,11 @@
       <c r="AK72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25159000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24362000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24144000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25219000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25909000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24285000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23789000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24737000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25179000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24767000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25037000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25226000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26220000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25599000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25302000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24844000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25831000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25696000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25384000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24740000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>25385000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24538000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24824000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24106000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24561000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23825000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24309000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>25015000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25886000</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH76" s="3">
         <v>74660000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>71496000</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1161000</v>
+      </c>
+      <c r="E81" s="3">
         <v>720000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-552000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-320000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1314000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>652000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-524000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1053000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>419000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-253000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-321000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>714000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>595000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-55000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-331000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>969000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>564000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>159000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>970000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>600000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>41000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-392000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>760000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>272000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-494000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-608000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>164000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-531000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5121000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>694000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-107000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2188000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +7997,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E83" s="3">
         <v>134000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>138000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>136000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>138000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>130000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>137000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>132000</v>
       </c>
       <c r="K83" s="3">
         <v>132000</v>
       </c>
       <c r="L83" s="3">
+        <v>132000</v>
+      </c>
+      <c r="M83" s="3">
         <v>127000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O83" s="3">
         <v>132000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>123000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>128000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>304000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>310000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>302000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>307000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>317000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>309000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>313000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>304000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>309000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>285000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>300000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>283000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>289000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>226000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>358000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>726000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>698000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>682000</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ83" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-466000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2891000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4375000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>193000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>947000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2109000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4173000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>130000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>451000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2609000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4373000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-105000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>812000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3311000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3018000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-525000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1109000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2730000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3546000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-176000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1307000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1950000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3301000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-368000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1061000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1930000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3373000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1215000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>453000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1541000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3263000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1190000</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK89" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +8807,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-222000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-157000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-118000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-94000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-181000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-154000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-114000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-148000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-183000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-162000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-99000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-151000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-145000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-142000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-139000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-179000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-160000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-144000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-132000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-137000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-99000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-128000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-148000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-181000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-171000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-663000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-481000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-352000</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ91" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK91" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-170000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-77000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-188000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-157000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-164000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-34000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-123000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-161000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-35000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-270000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-214000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-229000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-33000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1511000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-193000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-31000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-404000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-161000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-184000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-53000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>36000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-229000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-193000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-122000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-130000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>60000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-290000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-172000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-502000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-277000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ94" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK94" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,73 +9287,74 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>121000</v>
+        <v>120000</v>
       </c>
       <c r="E96" s="3">
         <v>121000</v>
       </c>
       <c r="F96" s="3">
+        <v>121000</v>
+      </c>
+      <c r="G96" s="3">
         <v>122000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>116000</v>
       </c>
       <c r="H96" s="3">
         <v>116000</v>
       </c>
       <c r="I96" s="3">
+        <v>116000</v>
+      </c>
+      <c r="J96" s="3">
         <v>118000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>117000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>111000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>112000</v>
       </c>
       <c r="M96" s="3">
         <v>112000</v>
       </c>
       <c r="N96" s="3">
+        <v>112000</v>
+      </c>
+      <c r="O96" s="3">
         <v>114000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>106000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>107000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-107000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-108000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-101000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-102000</v>
       </c>
       <c r="U96" s="3">
         <v>-102000</v>
       </c>
       <c r="V96" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-103000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-95000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-97000</v>
       </c>
       <c r="Y96" s="3">
         <v>-97000</v>
@@ -9138,7 +9372,7 @@
         <v>-97000</v>
       </c>
       <c r="AD96" s="3">
-        <v>0</v>
+        <v>-97000</v>
       </c>
       <c r="AE96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9725,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1141000</v>
+      </c>
+      <c r="E100" s="3">
         <v>389000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2198000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>367000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-808000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>995000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3336000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>619000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-248000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1766000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3702000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>224000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>105000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3274000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1843000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>557000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-608000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>714000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1631000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>392000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-848000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>821000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2392000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>481000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-130000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2344000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3690000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1446000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1997000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1312000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2033000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>621000</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ100" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK100" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E101" s="3">
         <v>21000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-48000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>27000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-41000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-31000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-75000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-77000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O101" s="3">
         <v>-179000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-85000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>17000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-179000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-85000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-31000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-58000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-64000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>36000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>71000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>31000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>22000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>30000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-54000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>20000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-57000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-84000</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ101" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK101" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL101" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>478000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2584000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1988000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>420000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1127000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>666000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>615000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>127000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1144000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>382000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-187000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>895000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1550000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>999000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-151000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>385000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2451000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1696000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-32000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>442000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1143000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>751000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-49000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>831000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>167000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-227000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-113000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1800000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-711000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>896000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-883000</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ102" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
